--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D6FCEB-D083-4D48-A8A8-6D96F6D6ECA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF761C-3C0F-4158-B734-31C4D55520D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,10 +447,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -458,10 +460,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -469,23 +475,17 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1541,80 +1541,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
-      <c r="AB1" s="37" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="AC1" s="34"/>
-      <c r="AD1" s="34"/>
-      <c r="AE1" s="34"/>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="34"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
     </row>
     <row r="2" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="34"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="38" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="34"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
+      <c r="AC2" s="25"/>
+      <c r="AD2" s="25"/>
+      <c r="AE2" s="25"/>
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
     </row>
     <row r="3" spans="1:33" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="19"/>
@@ -1652,49 +1652,49 @@
       <c r="AG3" s="17"/>
     </row>
     <row r="4" spans="1:33" s="14" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="39"/>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="39"/>
-      <c r="AA4" s="39"/>
-      <c r="AB4" s="39"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="40"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="32"/>
     </row>
     <row r="5" spans="1:33" s="14" customFormat="1" ht="13.5" customHeight="1">
       <c r="A5" s="27"/>
-      <c r="B5" s="25"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="15">
         <v>1</v>
       </c>
@@ -2202,7 +2202,7 @@
       <c r="X16" s="28"/>
       <c r="Y16" s="28"/>
       <c r="Z16" s="28"/>
-      <c r="AA16" s="36"/>
+      <c r="AA16" s="38"/>
       <c r="AB16" s="28"/>
       <c r="AC16" s="28"/>
       <c r="AD16" s="28"/>
@@ -2317,26 +2317,26 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:33" ht="207.75" customHeight="1">
+    <row r="21" spans="2:33" ht="279" customHeight="1">
       <c r="B21" s="23"/>
     </row>
     <row r="22" spans="2:33" ht="21" customHeight="1">
       <c r="AA22" s="5"/>
       <c r="AB22" s="5"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="37"/>
+      <c r="AE22" s="37"/>
+      <c r="AF22" s="37"/>
+      <c r="AG22" s="37"/>
     </row>
     <row r="23" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC23" s="31" t="s">
+      <c r="AC23" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="AD23" s="32"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="32"/>
-      <c r="AG23" s="32"/>
+      <c r="AD23" s="34"/>
+      <c r="AE23" s="34"/>
+      <c r="AF23" s="34"/>
+      <c r="AG23" s="34"/>
     </row>
     <row r="24" spans="2:33" ht="7.5" customHeight="1">
       <c r="D24" s="4"/>
@@ -2349,6 +2349,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="AD18:AD19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="T18:T19"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:L17"/>
+    <mergeCell ref="AB18:AB19"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="V18:V19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="AC23:AG23"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="AG18:AG19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="AF18:AF19"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="I16:I17"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="O18:O19"/>
     <mergeCell ref="AC16:AC17"/>
@@ -2365,60 +2419,6 @@
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="O16:O17"/>
     <mergeCell ref="U16:U17"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="AC23:AG23"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="U18:U19"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="AC22:AG22"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="AG18:AG19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="AF18:AF19"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="AD18:AD19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="T18:T19"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:L17"/>
-    <mergeCell ref="AB18:AB19"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="V18:V19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="I16:I17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0" bottom="0" header="0.31496062992125978" footer="0.31496062992125978"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF761C-3C0F-4158-B734-31C4D55520D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5617E719-B1AE-4B06-8B1F-893E29C267E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -444,37 +444,30 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -482,10 +475,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1541,80 +1541,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="24" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
     </row>
     <row r="2" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="29" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="25"/>
-      <c r="AG2" s="25"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
+      <c r="AG2" s="29"/>
     </row>
     <row r="3" spans="1:33" s="16" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="19"/>
@@ -1655,46 +1655,46 @@
       <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="25" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="31"/>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="32"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+      <c r="AC4" s="38"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="39"/>
     </row>
     <row r="5" spans="1:33" s="14" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="27"/>
-      <c r="B5" s="40"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="26"/>
       <c r="C5" s="15">
         <v>1</v>
       </c>
@@ -2178,139 +2178,139 @@
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="28"/>
-      <c r="W16" s="28"/>
-      <c r="X16" s="28"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="38"/>
-      <c r="AB16" s="28"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="28"/>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="28"/>
-      <c r="AG16" s="28"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="27"/>
+      <c r="AE16" s="27"/>
+      <c r="AF16" s="27"/>
+      <c r="AG16" s="27"/>
     </row>
     <row r="17" spans="2:33" ht="22.5" customHeight="1">
       <c r="B17" s="6"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="27"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="27"/>
-      <c r="Y17" s="27"/>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="27"/>
-      <c r="AB17" s="27"/>
-      <c r="AC17" s="27"/>
-      <c r="AD17" s="27"/>
-      <c r="AE17" s="27"/>
-      <c r="AF17" s="27"/>
-      <c r="AG17" s="27"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
     </row>
     <row r="18" spans="2:33" ht="22.5" customHeight="1">
       <c r="B18" s="6"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="26"/>
-      <c r="W18" s="26"/>
-      <c r="X18" s="26"/>
-      <c r="Y18" s="26"/>
-      <c r="Z18" s="26"/>
-      <c r="AA18" s="26"/>
-      <c r="AB18" s="26"/>
-      <c r="AC18" s="26"/>
-      <c r="AD18" s="26"/>
-      <c r="AE18" s="26"/>
-      <c r="AF18" s="26"/>
-      <c r="AG18" s="26"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="23"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
+      <c r="AE18" s="23"/>
+      <c r="AF18" s="23"/>
+      <c r="AG18" s="23"/>
     </row>
     <row r="19" spans="2:33" ht="22.5" customHeight="1">
       <c r="B19" s="6"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
-      <c r="AA19" s="27"/>
-      <c r="AB19" s="27"/>
-      <c r="AC19" s="27"/>
-      <c r="AD19" s="27"/>
-      <c r="AE19" s="27"/>
-      <c r="AF19" s="27"/>
-      <c r="AG19" s="27"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="24"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="24"/>
+      <c r="X19" s="24"/>
+      <c r="Y19" s="24"/>
+      <c r="Z19" s="24"/>
+      <c r="AA19" s="24"/>
+      <c r="AB19" s="24"/>
+      <c r="AC19" s="24"/>
+      <c r="AD19" s="24"/>
+      <c r="AE19" s="24"/>
+      <c r="AF19" s="24"/>
+      <c r="AG19" s="24"/>
     </row>
     <row r="20" spans="2:33" ht="19.5" customHeight="1">
       <c r="B20" s="21" t="s">
@@ -2318,25 +2318,56 @@
       </c>
     </row>
     <row r="21" spans="2:33" ht="279" customHeight="1">
-      <c r="B21" s="23"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="40"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="40"/>
+      <c r="S21" s="40"/>
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="40"/>
+      <c r="Y21" s="40"/>
+      <c r="Z21" s="40"/>
+      <c r="AA21" s="40"/>
+      <c r="AB21" s="40"/>
+      <c r="AC21" s="40"/>
+      <c r="AD21" s="40"/>
+      <c r="AE21" s="40"/>
+      <c r="AF21" s="40"/>
+      <c r="AG21" s="40"/>
     </row>
     <row r="22" spans="2:33" ht="21" customHeight="1">
       <c r="AA22" s="5"/>
       <c r="AB22" s="5"/>
-      <c r="AC22" s="36"/>
-      <c r="AD22" s="37"/>
-      <c r="AE22" s="37"/>
-      <c r="AF22" s="37"/>
-      <c r="AG22" s="37"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="34"/>
     </row>
     <row r="23" spans="2:33" ht="29.25" customHeight="1">
-      <c r="AC23" s="33" t="s">
+      <c r="AC23" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="AD23" s="34"/>
-      <c r="AE23" s="34"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="34"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
+      <c r="AG23" s="32"/>
     </row>
     <row r="24" spans="2:33" ht="7.5" customHeight="1">
       <c r="D24" s="4"/>
@@ -2348,7 +2379,62 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="B21:AG21"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AC18:AC19"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="AE18:AE19"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="M16:M17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="AC23:AG23"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="X18:X19"/>
+    <mergeCell ref="AC22:AG22"/>
+    <mergeCell ref="AG18:AG19"/>
+    <mergeCell ref="Y18:Y19"/>
+    <mergeCell ref="AA18:AA19"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="AF18:AF19"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="U18:U19"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="W18:W19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="S16:S17"/>
     <mergeCell ref="Z18:Z19"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="AD18:AD19"/>
@@ -2365,60 +2451,6 @@
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="H18:H19"/>
     <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="U18:U19"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="W18:W19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="AC23:AG23"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="X18:X19"/>
-    <mergeCell ref="AC22:AG22"/>
-    <mergeCell ref="AG18:AG19"/>
-    <mergeCell ref="Y18:Y19"/>
-    <mergeCell ref="AA18:AA19"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="AF18:AF19"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="M16:M17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="AC18:AC19"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="AE18:AE19"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="AE16:AE17"/>
-    <mergeCell ref="AG16:AG17"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="U16:U17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0" bottom="0" header="0.31496062992125978" footer="0.31496062992125978"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -1777,8 +1777,16 @@
       <c r="AB6" s="20" t="n"/>
       <c r="AC6" s="20" t="n"/>
       <c r="AD6" s="20" t="n"/>
-      <c r="AE6" s="20" t="n"/>
-      <c r="AF6" s="20" t="n"/>
+      <c r="AE6" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="20" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1818,8 +1826,16 @@
       <c r="AB7" s="20" t="n"/>
       <c r="AC7" s="20" t="n"/>
       <c r="AD7" s="20" t="n"/>
-      <c r="AE7" s="20" t="n"/>
-      <c r="AF7" s="20" t="n"/>
+      <c r="AE7" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF7" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AG7" s="20" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1859,8 +1875,16 @@
       <c r="AB8" s="20" t="n"/>
       <c r="AC8" s="20" t="n"/>
       <c r="AD8" s="20" t="n"/>
-      <c r="AE8" s="20" t="n"/>
-      <c r="AF8" s="20" t="n"/>
+      <c r="AE8" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF8" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AG8" s="20" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1900,8 +1924,16 @@
       <c r="AB9" s="20" t="n"/>
       <c r="AC9" s="20" t="n"/>
       <c r="AD9" s="20" t="n"/>
-      <c r="AE9" s="20" t="n"/>
-      <c r="AF9" s="20" t="n"/>
+      <c r="AE9" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="20" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -1941,8 +1973,16 @@
       <c r="AB10" s="20" t="n"/>
       <c r="AC10" s="20" t="n"/>
       <c r="AD10" s="20" t="n"/>
-      <c r="AE10" s="20" t="n"/>
-      <c r="AF10" s="20" t="n"/>
+      <c r="AE10" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="20" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1982,8 +2022,16 @@
       <c r="AB11" s="20" t="n"/>
       <c r="AC11" s="20" t="n"/>
       <c r="AD11" s="20" t="n"/>
-      <c r="AE11" s="20" t="n"/>
-      <c r="AF11" s="20" t="n"/>
+      <c r="AE11" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF11" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG11" s="20" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2023,8 +2071,16 @@
       <c r="AB12" s="20" t="n"/>
       <c r="AC12" s="20" t="n"/>
       <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="20" t="n"/>
-      <c r="AF12" s="20" t="n"/>
+      <c r="AE12" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG12" s="20" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2064,8 +2120,16 @@
       <c r="AB13" s="20" t="n"/>
       <c r="AC13" s="20" t="n"/>
       <c r="AD13" s="20" t="n"/>
-      <c r="AE13" s="20" t="n"/>
-      <c r="AF13" s="20" t="n"/>
+      <c r="AE13" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG13" s="20" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2105,8 +2169,16 @@
       <c r="AB14" s="20" t="n"/>
       <c r="AC14" s="20" t="n"/>
       <c r="AD14" s="20" t="n"/>
-      <c r="AE14" s="20" t="n"/>
-      <c r="AF14" s="20" t="n"/>
+      <c r="AE14" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF14" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG14" s="20" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2175,8 +2247,16 @@
       <c r="AB16" s="27" t="n"/>
       <c r="AC16" s="27" t="n"/>
       <c r="AD16" s="27" t="n"/>
-      <c r="AE16" s="27" t="n"/>
-      <c r="AF16" s="27" t="n"/>
+      <c r="AE16" s="35" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
+      <c r="AF16" s="35" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="AG16" s="27" t="n"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
@@ -2289,7 +2369,7 @@
       </c>
     </row>
     <row r="21" ht="279" customHeight="1">
-      <c r="B21" s="40" t="n"/>
+      <c r="B21" s="40" t="inlineStr"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="AA22" s="5" t="n"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -342,7 +342,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -439,6 +439,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1749,45 +1752,37 @@
           <t xml:space="preserve">การ Worm spindle และ TABLE SLIDE </t>
         </is>
       </c>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="20" t="n"/>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="20" t="n"/>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="20" t="n"/>
-      <c r="O6" s="20" t="n"/>
-      <c r="P6" s="20" t="n"/>
-      <c r="Q6" s="20" t="n"/>
-      <c r="R6" s="20" t="n"/>
-      <c r="S6" s="20" t="n"/>
-      <c r="T6" s="20" t="n"/>
-      <c r="U6" s="20" t="n"/>
-      <c r="V6" s="20" t="n"/>
-      <c r="W6" s="20" t="n"/>
-      <c r="X6" s="20" t="n"/>
-      <c r="Y6" s="20" t="n"/>
-      <c r="Z6" s="20" t="n"/>
-      <c r="AA6" s="30" t="n"/>
-      <c r="AB6" s="20" t="n"/>
-      <c r="AC6" s="20" t="n"/>
-      <c r="AD6" s="20" t="n"/>
-      <c r="AE6" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="20" t="n"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="20" t="inlineStr"/>
+      <c r="W6" s="20" t="inlineStr"/>
+      <c r="X6" s="20" t="inlineStr"/>
+      <c r="Y6" s="20" t="inlineStr"/>
+      <c r="Z6" s="20" t="inlineStr"/>
+      <c r="AA6" s="30" t="inlineStr"/>
+      <c r="AB6" s="20" t="inlineStr"/>
+      <c r="AC6" s="20" t="inlineStr"/>
+      <c r="AD6" s="20" t="inlineStr"/>
+      <c r="AE6" s="30" t="inlineStr"/>
+      <c r="AF6" s="30" t="inlineStr"/>
+      <c r="AG6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="n">
@@ -1798,45 +1793,37 @@
           <t>เช็คระดับนำมันไฮดรอลิก และ การทำงานของ PUMP</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="20" t="n"/>
-      <c r="P7" s="20" t="n"/>
-      <c r="Q7" s="20" t="n"/>
-      <c r="R7" s="20" t="n"/>
-      <c r="S7" s="20" t="n"/>
-      <c r="T7" s="20" t="n"/>
-      <c r="U7" s="20" t="n"/>
-      <c r="V7" s="20" t="n"/>
-      <c r="W7" s="20" t="n"/>
-      <c r="X7" s="20" t="n"/>
-      <c r="Y7" s="20" t="n"/>
-      <c r="Z7" s="20" t="n"/>
-      <c r="AA7" s="30" t="n"/>
-      <c r="AB7" s="20" t="n"/>
-      <c r="AC7" s="20" t="n"/>
-      <c r="AD7" s="20" t="n"/>
-      <c r="AE7" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF7" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG7" s="20" t="n"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="20" t="inlineStr"/>
+      <c r="W7" s="20" t="inlineStr"/>
+      <c r="X7" s="20" t="inlineStr"/>
+      <c r="Y7" s="20" t="inlineStr"/>
+      <c r="Z7" s="20" t="inlineStr"/>
+      <c r="AA7" s="30" t="inlineStr"/>
+      <c r="AB7" s="20" t="inlineStr"/>
+      <c r="AC7" s="20" t="inlineStr"/>
+      <c r="AD7" s="20" t="inlineStr"/>
+      <c r="AE7" s="30" t="inlineStr"/>
+      <c r="AF7" s="30" t="inlineStr"/>
+      <c r="AG7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="11" t="n">
@@ -1847,45 +1834,37 @@
           <t>เช็คระดับของน้ำยา COOLANNT PUMP</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="20" t="n"/>
-      <c r="P8" s="20" t="n"/>
-      <c r="Q8" s="20" t="n"/>
-      <c r="R8" s="20" t="n"/>
-      <c r="S8" s="20" t="n"/>
-      <c r="T8" s="20" t="n"/>
-      <c r="U8" s="20" t="n"/>
-      <c r="V8" s="20" t="n"/>
-      <c r="W8" s="20" t="n"/>
-      <c r="X8" s="20" t="n"/>
-      <c r="Y8" s="20" t="n"/>
-      <c r="Z8" s="20" t="n"/>
-      <c r="AA8" s="30" t="n"/>
-      <c r="AB8" s="20" t="n"/>
-      <c r="AC8" s="20" t="n"/>
-      <c r="AD8" s="20" t="n"/>
-      <c r="AE8" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF8" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG8" s="20" t="n"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
+      <c r="K8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="inlineStr"/>
+      <c r="O8" s="20" t="inlineStr"/>
+      <c r="P8" s="20" t="inlineStr"/>
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="20" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="20" t="inlineStr"/>
+      <c r="W8" s="20" t="inlineStr"/>
+      <c r="X8" s="20" t="inlineStr"/>
+      <c r="Y8" s="20" t="inlineStr"/>
+      <c r="Z8" s="20" t="inlineStr"/>
+      <c r="AA8" s="30" t="inlineStr"/>
+      <c r="AB8" s="20" t="inlineStr"/>
+      <c r="AC8" s="20" t="inlineStr"/>
+      <c r="AD8" s="20" t="inlineStr"/>
+      <c r="AE8" s="30" t="inlineStr"/>
+      <c r="AF8" s="30" t="inlineStr"/>
+      <c r="AG8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="11" t="n">
@@ -1896,45 +1875,37 @@
           <t>ตรวจสอบการทำงานของแม่เหล็ก</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="20" t="n"/>
-      <c r="P9" s="20" t="n"/>
-      <c r="Q9" s="20" t="n"/>
-      <c r="R9" s="20" t="n"/>
-      <c r="S9" s="20" t="n"/>
-      <c r="T9" s="20" t="n"/>
-      <c r="U9" s="20" t="n"/>
-      <c r="V9" s="20" t="n"/>
-      <c r="W9" s="20" t="n"/>
-      <c r="X9" s="20" t="n"/>
-      <c r="Y9" s="20" t="n"/>
-      <c r="Z9" s="20" t="n"/>
-      <c r="AA9" s="30" t="n"/>
-      <c r="AB9" s="20" t="n"/>
-      <c r="AC9" s="20" t="n"/>
-      <c r="AD9" s="20" t="n"/>
-      <c r="AE9" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="20" t="n"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="20" t="inlineStr"/>
+      <c r="W9" s="20" t="inlineStr"/>
+      <c r="X9" s="20" t="inlineStr"/>
+      <c r="Y9" s="20" t="inlineStr"/>
+      <c r="Z9" s="20" t="inlineStr"/>
+      <c r="AA9" s="30" t="inlineStr"/>
+      <c r="AB9" s="20" t="inlineStr"/>
+      <c r="AC9" s="20" t="inlineStr"/>
+      <c r="AD9" s="20" t="inlineStr"/>
+      <c r="AE9" s="30" t="inlineStr"/>
+      <c r="AF9" s="30" t="inlineStr"/>
+      <c r="AG9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="11" t="n">
@@ -1945,45 +1916,37 @@
           <t>ตรวจสอบการทำงานของ SLIDE X,Y</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="20" t="n"/>
-      <c r="P10" s="20" t="n"/>
-      <c r="Q10" s="20" t="n"/>
-      <c r="R10" s="20" t="n"/>
-      <c r="S10" s="20" t="n"/>
-      <c r="T10" s="20" t="n"/>
-      <c r="U10" s="20" t="n"/>
-      <c r="V10" s="20" t="n"/>
-      <c r="W10" s="20" t="n"/>
-      <c r="X10" s="20" t="n"/>
-      <c r="Y10" s="20" t="n"/>
-      <c r="Z10" s="20" t="n"/>
-      <c r="AA10" s="30" t="n"/>
-      <c r="AB10" s="20" t="n"/>
-      <c r="AC10" s="20" t="n"/>
-      <c r="AD10" s="20" t="n"/>
-      <c r="AE10" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="20" t="n"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="20" t="inlineStr"/>
+      <c r="W10" s="20" t="inlineStr"/>
+      <c r="X10" s="20" t="inlineStr"/>
+      <c r="Y10" s="20" t="inlineStr"/>
+      <c r="Z10" s="20" t="inlineStr"/>
+      <c r="AA10" s="30" t="inlineStr"/>
+      <c r="AB10" s="20" t="inlineStr"/>
+      <c r="AC10" s="20" t="inlineStr"/>
+      <c r="AD10" s="20" t="inlineStr"/>
+      <c r="AE10" s="30" t="inlineStr"/>
+      <c r="AF10" s="30" t="inlineStr"/>
+      <c r="AG10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="11" t="n">
@@ -1994,45 +1957,37 @@
           <t>ตรวจสอบสภาพความพร้อมโดยรวมของเครื่องจักร</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="20" t="n"/>
-      <c r="P11" s="20" t="n"/>
-      <c r="Q11" s="20" t="n"/>
-      <c r="R11" s="20" t="n"/>
-      <c r="S11" s="20" t="n"/>
-      <c r="T11" s="20" t="n"/>
-      <c r="U11" s="20" t="n"/>
-      <c r="V11" s="20" t="n"/>
-      <c r="W11" s="20" t="n"/>
-      <c r="X11" s="20" t="n"/>
-      <c r="Y11" s="20" t="n"/>
-      <c r="Z11" s="20" t="n"/>
-      <c r="AA11" s="30" t="n"/>
-      <c r="AB11" s="20" t="n"/>
-      <c r="AC11" s="20" t="n"/>
-      <c r="AD11" s="20" t="n"/>
-      <c r="AE11" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF11" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG11" s="20" t="n"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr"/>
+      <c r="M11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="inlineStr"/>
+      <c r="O11" s="20" t="inlineStr"/>
+      <c r="P11" s="20" t="inlineStr"/>
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="20" t="inlineStr"/>
+      <c r="V11" s="20" t="inlineStr"/>
+      <c r="W11" s="20" t="inlineStr"/>
+      <c r="X11" s="20" t="inlineStr"/>
+      <c r="Y11" s="20" t="inlineStr"/>
+      <c r="Z11" s="20" t="inlineStr"/>
+      <c r="AA11" s="30" t="inlineStr"/>
+      <c r="AB11" s="20" t="inlineStr"/>
+      <c r="AC11" s="20" t="inlineStr"/>
+      <c r="AD11" s="20" t="inlineStr"/>
+      <c r="AE11" s="30" t="inlineStr"/>
+      <c r="AF11" s="30" t="inlineStr"/>
+      <c r="AG11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="11" t="n">
@@ -2043,45 +1998,37 @@
           <t>ตรวจสอบระดับน้ำมันของ PUMP น้ำมันหล่อลื่น</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="20" t="n"/>
-      <c r="P12" s="20" t="n"/>
-      <c r="Q12" s="20" t="n"/>
-      <c r="R12" s="20" t="n"/>
-      <c r="S12" s="20" t="n"/>
-      <c r="T12" s="20" t="n"/>
-      <c r="U12" s="20" t="n"/>
-      <c r="V12" s="20" t="n"/>
-      <c r="W12" s="20" t="n"/>
-      <c r="X12" s="20" t="n"/>
-      <c r="Y12" s="20" t="n"/>
-      <c r="Z12" s="20" t="n"/>
-      <c r="AA12" s="30" t="n"/>
-      <c r="AB12" s="20" t="n"/>
-      <c r="AC12" s="20" t="n"/>
-      <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF12" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG12" s="20" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="20" t="inlineStr"/>
+      <c r="W12" s="20" t="inlineStr"/>
+      <c r="X12" s="20" t="inlineStr"/>
+      <c r="Y12" s="20" t="inlineStr"/>
+      <c r="Z12" s="20" t="inlineStr"/>
+      <c r="AA12" s="30" t="inlineStr"/>
+      <c r="AB12" s="20" t="inlineStr"/>
+      <c r="AC12" s="20" t="inlineStr"/>
+      <c r="AD12" s="20" t="inlineStr"/>
+      <c r="AE12" s="30" t="inlineStr"/>
+      <c r="AF12" s="30" t="inlineStr"/>
+      <c r="AG12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -2092,45 +2039,37 @@
           <t>ตรวจสอบการทำงานของไฟฟ้าและแสงสว่าง</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="n"/>
-      <c r="O13" s="20" t="n"/>
-      <c r="P13" s="20" t="n"/>
-      <c r="Q13" s="20" t="n"/>
-      <c r="R13" s="20" t="n"/>
-      <c r="S13" s="20" t="n"/>
-      <c r="T13" s="20" t="n"/>
-      <c r="U13" s="20" t="n"/>
-      <c r="V13" s="20" t="n"/>
-      <c r="W13" s="20" t="n"/>
-      <c r="X13" s="20" t="n"/>
-      <c r="Y13" s="20" t="n"/>
-      <c r="Z13" s="20" t="n"/>
-      <c r="AA13" s="30" t="n"/>
-      <c r="AB13" s="20" t="n"/>
-      <c r="AC13" s="20" t="n"/>
-      <c r="AD13" s="20" t="n"/>
-      <c r="AE13" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF13" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG13" s="20" t="n"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="20" t="inlineStr"/>
+      <c r="W13" s="20" t="inlineStr"/>
+      <c r="X13" s="20" t="inlineStr"/>
+      <c r="Y13" s="20" t="inlineStr"/>
+      <c r="Z13" s="20" t="inlineStr"/>
+      <c r="AA13" s="30" t="inlineStr"/>
+      <c r="AB13" s="20" t="inlineStr"/>
+      <c r="AC13" s="20" t="inlineStr"/>
+      <c r="AD13" s="20" t="inlineStr"/>
+      <c r="AE13" s="30" t="inlineStr"/>
+      <c r="AF13" s="30" t="inlineStr"/>
+      <c r="AG13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="11" t="n">
@@ -2141,45 +2080,37 @@
           <t>ตรวจสอบการทำงานของตัวดูดอากศ</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="20" t="n"/>
-      <c r="O14" s="20" t="n"/>
-      <c r="P14" s="20" t="n"/>
-      <c r="Q14" s="20" t="n"/>
-      <c r="R14" s="20" t="n"/>
-      <c r="S14" s="20" t="n"/>
-      <c r="T14" s="20" t="n"/>
-      <c r="U14" s="20" t="n"/>
-      <c r="V14" s="20" t="n"/>
-      <c r="W14" s="20" t="n"/>
-      <c r="X14" s="20" t="n"/>
-      <c r="Y14" s="20" t="n"/>
-      <c r="Z14" s="20" t="n"/>
-      <c r="AA14" s="30" t="n"/>
-      <c r="AB14" s="20" t="n"/>
-      <c r="AC14" s="20" t="n"/>
-      <c r="AD14" s="20" t="n"/>
-      <c r="AE14" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF14" s="30" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG14" s="20" t="n"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
+      <c r="H14" s="20" t="inlineStr"/>
+      <c r="I14" s="20" t="inlineStr"/>
+      <c r="J14" s="20" t="inlineStr"/>
+      <c r="K14" s="20" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr"/>
+      <c r="M14" s="20" t="inlineStr"/>
+      <c r="N14" s="20" t="inlineStr"/>
+      <c r="O14" s="20" t="inlineStr"/>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
+      <c r="S14" s="20" t="inlineStr"/>
+      <c r="T14" s="20" t="inlineStr"/>
+      <c r="U14" s="20" t="inlineStr"/>
+      <c r="V14" s="20" t="inlineStr"/>
+      <c r="W14" s="20" t="inlineStr"/>
+      <c r="X14" s="20" t="inlineStr"/>
+      <c r="Y14" s="20" t="inlineStr"/>
+      <c r="Z14" s="20" t="inlineStr"/>
+      <c r="AA14" s="30" t="inlineStr"/>
+      <c r="AB14" s="20" t="inlineStr"/>
+      <c r="AC14" s="20" t="inlineStr"/>
+      <c r="AD14" s="20" t="inlineStr"/>
+      <c r="AE14" s="30" t="inlineStr"/>
+      <c r="AF14" s="30" t="inlineStr"/>
+      <c r="AG14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="10" t="n"/>
@@ -2219,45 +2150,37 @@
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="8" t="n"/>
       <c r="B16" s="7" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="27" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="27" t="n"/>
-      <c r="N16" s="27" t="n"/>
-      <c r="O16" s="27" t="n"/>
-      <c r="P16" s="27" t="n"/>
-      <c r="Q16" s="27" t="n"/>
-      <c r="R16" s="27" t="n"/>
-      <c r="S16" s="27" t="n"/>
-      <c r="T16" s="27" t="n"/>
-      <c r="U16" s="27" t="n"/>
-      <c r="V16" s="27" t="n"/>
-      <c r="W16" s="27" t="n"/>
-      <c r="X16" s="27" t="n"/>
-      <c r="Y16" s="27" t="n"/>
-      <c r="Z16" s="27" t="n"/>
-      <c r="AA16" s="35" t="n"/>
-      <c r="AB16" s="27" t="n"/>
-      <c r="AC16" s="27" t="n"/>
-      <c r="AD16" s="27" t="n"/>
-      <c r="AE16" s="35" t="inlineStr">
-        <is>
-          <t>ณัช วิกรัยเจริญ</t>
-        </is>
-      </c>
-      <c r="AF16" s="35" t="inlineStr">
-        <is>
-          <t>ณัช วิกรัยเจริญ</t>
-        </is>
-      </c>
-      <c r="AG16" s="27" t="n"/>
+      <c r="C16" s="27" t="inlineStr"/>
+      <c r="D16" s="27" t="inlineStr"/>
+      <c r="E16" s="27" t="inlineStr"/>
+      <c r="F16" s="27" t="inlineStr"/>
+      <c r="G16" s="27" t="inlineStr"/>
+      <c r="H16" s="27" t="inlineStr"/>
+      <c r="I16" s="27" t="inlineStr"/>
+      <c r="J16" s="27" t="inlineStr"/>
+      <c r="K16" s="27" t="inlineStr"/>
+      <c r="L16" s="27" t="inlineStr"/>
+      <c r="M16" s="27" t="inlineStr"/>
+      <c r="N16" s="27" t="inlineStr"/>
+      <c r="O16" s="27" t="inlineStr"/>
+      <c r="P16" s="27" t="inlineStr"/>
+      <c r="Q16" s="27" t="inlineStr"/>
+      <c r="R16" s="27" t="inlineStr"/>
+      <c r="S16" s="27" t="inlineStr"/>
+      <c r="T16" s="27" t="inlineStr"/>
+      <c r="U16" s="27" t="inlineStr"/>
+      <c r="V16" s="27" t="inlineStr"/>
+      <c r="W16" s="27" t="inlineStr"/>
+      <c r="X16" s="27" t="inlineStr"/>
+      <c r="Y16" s="27" t="inlineStr"/>
+      <c r="Z16" s="27" t="inlineStr"/>
+      <c r="AA16" s="35" t="inlineStr"/>
+      <c r="AB16" s="27" t="inlineStr"/>
+      <c r="AC16" s="27" t="inlineStr"/>
+      <c r="AD16" s="27" t="inlineStr"/>
+      <c r="AE16" s="35" t="inlineStr"/>
+      <c r="AF16" s="35" t="inlineStr"/>
+      <c r="AG16" s="27" t="inlineStr"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="B17" s="6" t="n"/>
@@ -2295,37 +2218,37 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="B18" s="6" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="23" t="n"/>
-      <c r="H18" s="23" t="n"/>
-      <c r="I18" s="23" t="n"/>
-      <c r="J18" s="23" t="n"/>
-      <c r="K18" s="23" t="n"/>
-      <c r="L18" s="23" t="n"/>
-      <c r="M18" s="23" t="n"/>
-      <c r="N18" s="23" t="n"/>
-      <c r="O18" s="23" t="n"/>
-      <c r="P18" s="23" t="n"/>
-      <c r="Q18" s="23" t="n"/>
-      <c r="R18" s="23" t="n"/>
-      <c r="S18" s="23" t="n"/>
-      <c r="T18" s="23" t="n"/>
-      <c r="U18" s="23" t="n"/>
-      <c r="V18" s="23" t="n"/>
-      <c r="W18" s="23" t="n"/>
-      <c r="X18" s="23" t="n"/>
-      <c r="Y18" s="23" t="n"/>
-      <c r="Z18" s="23" t="n"/>
-      <c r="AA18" s="23" t="n"/>
-      <c r="AB18" s="23" t="n"/>
-      <c r="AC18" s="23" t="n"/>
-      <c r="AD18" s="23" t="n"/>
-      <c r="AE18" s="23" t="n"/>
-      <c r="AF18" s="23" t="n"/>
-      <c r="AG18" s="23" t="n"/>
+      <c r="C18" s="23" t="inlineStr"/>
+      <c r="D18" s="23" t="inlineStr"/>
+      <c r="E18" s="23" t="inlineStr"/>
+      <c r="F18" s="23" t="inlineStr"/>
+      <c r="G18" s="23" t="inlineStr"/>
+      <c r="H18" s="23" t="inlineStr"/>
+      <c r="I18" s="23" t="inlineStr"/>
+      <c r="J18" s="23" t="inlineStr"/>
+      <c r="K18" s="23" t="inlineStr"/>
+      <c r="L18" s="23" t="inlineStr"/>
+      <c r="M18" s="23" t="inlineStr"/>
+      <c r="N18" s="23" t="inlineStr"/>
+      <c r="O18" s="23" t="inlineStr"/>
+      <c r="P18" s="23" t="inlineStr"/>
+      <c r="Q18" s="23" t="inlineStr"/>
+      <c r="R18" s="23" t="inlineStr"/>
+      <c r="S18" s="23" t="inlineStr"/>
+      <c r="T18" s="23" t="inlineStr"/>
+      <c r="U18" s="23" t="inlineStr"/>
+      <c r="V18" s="23" t="inlineStr"/>
+      <c r="W18" s="23" t="inlineStr"/>
+      <c r="X18" s="23" t="inlineStr"/>
+      <c r="Y18" s="23" t="inlineStr"/>
+      <c r="Z18" s="23" t="inlineStr"/>
+      <c r="AA18" s="23" t="inlineStr"/>
+      <c r="AB18" s="23" t="inlineStr"/>
+      <c r="AC18" s="23" t="inlineStr"/>
+      <c r="AD18" s="23" t="inlineStr"/>
+      <c r="AE18" s="23" t="inlineStr"/>
+      <c r="AF18" s="23" t="inlineStr"/>
+      <c r="AG18" s="23" t="inlineStr"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="B19" s="6" t="n"/>
@@ -2369,7 +2292,7 @@
       </c>
     </row>
     <row r="21" ht="279" customHeight="1">
-      <c r="B21" s="40" t="inlineStr"/>
+      <c r="B21" s="41" t="inlineStr"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="AA22" s="5" t="n"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -1757,7 +1757,11 @@
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
       <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="20" t="inlineStr"/>
       <c r="J6" s="20" t="inlineStr"/>
       <c r="K6" s="20" t="inlineStr"/>
@@ -1798,7 +1802,11 @@
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
       <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
       <c r="K7" s="20" t="inlineStr"/>
@@ -1839,7 +1847,11 @@
       <c r="E8" s="20" t="inlineStr"/>
       <c r="F8" s="20" t="inlineStr"/>
       <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I8" s="20" t="inlineStr"/>
       <c r="J8" s="20" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr"/>
@@ -1880,7 +1892,11 @@
       <c r="E9" s="20" t="inlineStr"/>
       <c r="F9" s="20" t="inlineStr"/>
       <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="20" t="inlineStr"/>
       <c r="J9" s="20" t="inlineStr"/>
       <c r="K9" s="20" t="inlineStr"/>
@@ -1921,7 +1937,11 @@
       <c r="E10" s="20" t="inlineStr"/>
       <c r="F10" s="20" t="inlineStr"/>
       <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="H10" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
       <c r="K10" s="20" t="inlineStr"/>
@@ -1962,7 +1982,11 @@
       <c r="E11" s="20" t="inlineStr"/>
       <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="H11" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="20" t="inlineStr"/>
       <c r="J11" s="20" t="inlineStr"/>
       <c r="K11" s="20" t="inlineStr"/>
@@ -2003,7 +2027,11 @@
       <c r="E12" s="20" t="inlineStr"/>
       <c r="F12" s="20" t="inlineStr"/>
       <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
+      <c r="H12" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="20" t="inlineStr"/>
       <c r="J12" s="20" t="inlineStr"/>
       <c r="K12" s="20" t="inlineStr"/>
@@ -2044,7 +2072,11 @@
       <c r="E13" s="20" t="inlineStr"/>
       <c r="F13" s="20" t="inlineStr"/>
       <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
+      <c r="H13" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
       <c r="K13" s="20" t="inlineStr"/>
@@ -2085,7 +2117,11 @@
       <c r="E14" s="20" t="inlineStr"/>
       <c r="F14" s="20" t="inlineStr"/>
       <c r="G14" s="20" t="inlineStr"/>
-      <c r="H14" s="20" t="inlineStr"/>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
       <c r="K14" s="20" t="inlineStr"/>
@@ -2155,7 +2191,11 @@
       <c r="E16" s="27" t="inlineStr"/>
       <c r="F16" s="27" t="inlineStr"/>
       <c r="G16" s="27" t="inlineStr"/>
-      <c r="H16" s="27" t="inlineStr"/>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="I16" s="27" t="inlineStr"/>
       <c r="J16" s="27" t="inlineStr"/>
       <c r="K16" s="27" t="inlineStr"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -1762,7 +1762,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="I6" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="20" t="inlineStr"/>
       <c r="K6" s="20" t="inlineStr"/>
       <c r="L6" s="20" t="inlineStr"/>
@@ -1807,7 +1811,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="20" t="inlineStr"/>
       <c r="K7" s="20" t="inlineStr"/>
       <c r="L7" s="20" t="inlineStr"/>
@@ -1852,7 +1860,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
+      <c r="I8" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="20" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr"/>
       <c r="L8" s="20" t="inlineStr"/>
@@ -1897,7 +1909,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="20" t="inlineStr"/>
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
@@ -1942,7 +1958,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
+      <c r="I10" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="20" t="inlineStr"/>
       <c r="K10" s="20" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr"/>
@@ -1987,7 +2007,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
+      <c r="I11" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="20" t="inlineStr"/>
       <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr"/>
@@ -2032,7 +2056,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="20" t="inlineStr"/>
       <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
@@ -2077,7 +2105,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I13" s="20" t="inlineStr"/>
+      <c r="I13" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J13" s="20" t="inlineStr"/>
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="inlineStr"/>
@@ -2122,7 +2154,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr"/>
+      <c r="I14" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J14" s="20" t="inlineStr"/>
       <c r="K14" s="20" t="inlineStr"/>
       <c r="L14" s="20" t="inlineStr"/>
@@ -2196,7 +2232,11 @@
           <t>ณัช วิกรัยเจริญ</t>
         </is>
       </c>
-      <c r="I16" s="27" t="inlineStr"/>
+      <c r="I16" s="35" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="J16" s="27" t="inlineStr"/>
       <c r="K16" s="27" t="inlineStr"/>
       <c r="L16" s="27" t="inlineStr"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -342,7 +342,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -442,6 +442,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2303,7 +2306,11 @@
       <c r="E18" s="23" t="inlineStr"/>
       <c r="F18" s="23" t="inlineStr"/>
       <c r="G18" s="23" t="inlineStr"/>
-      <c r="H18" s="23" t="inlineStr"/>
+      <c r="H18" s="42" t="inlineStr">
+        <is>
+          <t>รัชพล</t>
+        </is>
+      </c>
       <c r="I18" s="23" t="inlineStr"/>
       <c r="J18" s="23" t="inlineStr"/>
       <c r="K18" s="23" t="inlineStr"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -1770,7 +1770,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="J6" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="20" t="inlineStr"/>
       <c r="L6" s="20" t="inlineStr"/>
       <c r="M6" s="20" t="inlineStr"/>
@@ -1819,7 +1823,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K7" s="20" t="inlineStr"/>
       <c r="L7" s="20" t="inlineStr"/>
       <c r="M7" s="20" t="inlineStr"/>
@@ -1868,7 +1876,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="J8" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K8" s="20" t="inlineStr"/>
       <c r="L8" s="20" t="inlineStr"/>
       <c r="M8" s="20" t="inlineStr"/>
@@ -1917,7 +1929,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
       <c r="M9" s="20" t="inlineStr"/>
@@ -1966,7 +1982,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="J10" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="20" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr"/>
       <c r="M10" s="20" t="inlineStr"/>
@@ -2015,7 +2035,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="J11" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr"/>
       <c r="M11" s="20" t="inlineStr"/>
@@ -2064,7 +2088,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="J12" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
       <c r="M12" s="20" t="inlineStr"/>
@@ -2113,7 +2141,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr"/>
+      <c r="J13" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K13" s="20" t="inlineStr"/>
       <c r="L13" s="20" t="inlineStr"/>
       <c r="M13" s="20" t="inlineStr"/>
@@ -2162,7 +2194,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr"/>
+      <c r="J14" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K14" s="20" t="inlineStr"/>
       <c r="L14" s="20" t="inlineStr"/>
       <c r="M14" s="20" t="inlineStr"/>
@@ -2240,7 +2276,11 @@
           <t>ณัช วิกรัยเจริญ</t>
         </is>
       </c>
-      <c r="J16" s="27" t="inlineStr"/>
+      <c r="J16" s="35" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="K16" s="27" t="inlineStr"/>
       <c r="L16" s="27" t="inlineStr"/>
       <c r="M16" s="27" t="inlineStr"/>

--- a/FM-MN-07_GRINDING-02.xlsx
+++ b/FM-MN-07_GRINDING-02.xlsx
@@ -1776,7 +1776,11 @@
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
+      <c r="L6" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="20" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr"/>
       <c r="O6" s="20" t="inlineStr"/>
@@ -1829,7 +1833,11 @@
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M7" s="20" t="inlineStr"/>
       <c r="N7" s="20" t="inlineStr"/>
       <c r="O7" s="20" t="inlineStr"/>
@@ -1882,7 +1890,11 @@
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr"/>
+      <c r="L8" s="30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M8" s="20" t="inlineStr"/>
       <c r="N8" s="20" t="inlineStr"/>
       <c r="O8" s="20" t="inlineStr"/>
@@ -1935,7 +1947,11 @@
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
+      <c r="L9" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="20" t="inlineStr"/>
       <c r="N9" s="20" t="inlineStr"/>
       <c r="O9" s="20" t="inlineStr"/>
@@ -1988,7 +2004,11 @@
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
+      <c r="L10" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="20" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr"/>
       <c r="O10" s="20" t="inlineStr"/>
@@ -2041,7 +2061,11 @@
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr"/>
+      <c r="L11" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="20" t="inlineStr"/>
       <c r="N11" s="20" t="inlineStr"/>
       <c r="O11" s="20" t="inlineStr"/>
@@ -2094,7 +2118,11 @@
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
+      <c r="L12" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="20" t="inlineStr"/>
       <c r="N12" s="20" t="inlineStr"/>
       <c r="O12" s="20" t="inlineStr"/>
@@ -2147,7 +2175,11 @@
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
+      <c r="L13" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M13" s="20" t="inlineStr"/>
       <c r="N13" s="20" t="inlineStr"/>
       <c r="O13" s="20" t="inlineStr"/>
@@ -2200,7 +2232,11 @@
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr"/>
+      <c r="L14" s="30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
@@ -2282,7 +2318,11 @@
         </is>
       </c>
       <c r="K16" s="27" t="inlineStr"/>
-      <c r="L16" s="27" t="inlineStr"/>
+      <c r="L16" s="35" t="inlineStr">
+        <is>
+          <t>ณัช วิกรัยเจริญ</t>
+        </is>
+      </c>
       <c r="M16" s="27" t="inlineStr"/>
       <c r="N16" s="27" t="inlineStr"/>
       <c r="O16" s="27" t="inlineStr"/>
